--- a/api/data/examples/folgas.xlsx
+++ b/api/data/examples/folgas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/projeto-intranet/api/data/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3943FAE-1742-B94C-8F9B-94D056421017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122A6EE-180D-3B45-892D-5E61953EA386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{67A2EEE8-9748-8D48-BF2B-81AAAD5C4461}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Funcionário</t>
   </si>
@@ -47,7 +47,76 @@
     <t>Kamila</t>
   </si>
   <si>
-    <t>21, 29</t>
+    <t>Joana</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>Samantha</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Yuri</t>
+  </si>
+  <si>
+    <t>Camilla C</t>
+  </si>
+  <si>
+    <t>Danielle</t>
+  </si>
+  <si>
+    <t>Luiza</t>
+  </si>
+  <si>
+    <t>Tamiris</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>Thais C</t>
+  </si>
+  <si>
+    <t>ferias</t>
+  </si>
+  <si>
+    <t>14/06/2026, 28/06/2026</t>
+  </si>
+  <si>
+    <t>13/06/2026, 27,06,2026</t>
+  </si>
+  <si>
+    <t>07/06/2026, 21/06/2026</t>
+  </si>
+  <si>
+    <t>06/06/2026, 28/06/2026</t>
+  </si>
+  <si>
+    <t>03/06/2026, 07/06/2026 (anual 5 dias), 20/06/2026</t>
+  </si>
+  <si>
+    <t>09/06/2026, 13/06/2026 (anual 5 dias), 26/06/2026</t>
+  </si>
+  <si>
+    <t>14/06/2026, 30/06/2026</t>
+  </si>
+  <si>
+    <t>13/06/2026, 29/06/2026</t>
+  </si>
+  <si>
+    <t>11/06/2026, 27/06/2026</t>
+  </si>
+  <si>
+    <t>09/06/2026, 19/06/2026</t>
+  </si>
+  <si>
+    <t>13/06/2026, 21/06/2026</t>
   </si>
 </sst>
 </file>
@@ -426,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68866D42-A9D1-DF4D-85BC-38A358C8AC3C}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -443,19 +512,107 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/api/data/examples/folgas.xlsx
+++ b/api/data/examples/folgas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/projeto-intranet/api/data/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122A6EE-180D-3B45-892D-5E61953EA386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7C3165-92BD-8148-A59B-4070121EF09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{67A2EEE8-9748-8D48-BF2B-81AAAD5C4461}"/>
   </bookViews>

--- a/api/data/examples/folgas.xlsx
+++ b/api/data/examples/folgas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bibianadibellacostabatista/Documents/Thais/Igen/intranet-pasta/projeto-intranet/api/data/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7C3165-92BD-8148-A59B-4070121EF09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E831D209-3C3D-5142-8E25-EB5DBDDEFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{67A2EEE8-9748-8D48-BF2B-81AAAD5C4461}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>Funcionário</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Dias de Folga (Ex: 01, 05, 10)</t>
   </si>
   <si>
-    <t>Kamila</t>
-  </si>
-  <si>
     <t>Joana</t>
   </si>
   <si>
@@ -117,6 +114,36 @@
   </si>
   <si>
     <t>13/06/2026, 21/06/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026, 26/07/2026</t>
+  </si>
+  <si>
+    <t>11/07/2026, 25/07/2026</t>
+  </si>
+  <si>
+    <t>18/07/2026 e férias</t>
+  </si>
+  <si>
+    <t>06/07/2026, 18/07/2026</t>
+  </si>
+  <si>
+    <t>04/07/2026, 16/07/2026</t>
+  </si>
+  <si>
+    <t>08/07/2026, 26/07/2026, 31/07/2026, 04/08/2026 (anual 5 dias)</t>
+  </si>
+  <si>
+    <t>09/07/2026, 19/07/2026</t>
+  </si>
+  <si>
+    <t>02/07/2026, 06/07/2026 (annual 5 dias), 17/07/2026</t>
+  </si>
+  <si>
+    <t>07/07/2026, ferias</t>
+  </si>
+  <si>
+    <t>04/07/2026, 18/07/2026</t>
   </si>
 </sst>
 </file>
@@ -158,9 +185,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,42 +524,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68866D42-A9D1-DF4D-85BC-38A358C8AC3C}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -538,7 +567,7 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -546,7 +575,7 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -554,7 +583,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -562,7 +591,7 @@
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -570,7 +599,7 @@
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -578,7 +607,7 @@
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -586,32 +615,120 @@
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
